--- a/artfynd/A 21044-2026 artfynd.xlsx
+++ b/artfynd/A 21044-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114571555</v>
+        <v>114571554</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582801</v>
+        <v>582858</v>
       </c>
       <c r="R2" t="n">
-        <v>6653337</v>
+        <v>6654115</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,58 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114567346</v>
+        <v>114571555</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582774</v>
+        <v>582801</v>
       </c>
       <c r="R3" t="n">
-        <v>6653720</v>
+        <v>6653337</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,16 +872,11 @@
         <v>114565008</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1002,6 +978,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114567346</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>582774</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6653720</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21044-2026 artfynd.xlsx
+++ b/artfynd/A 21044-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571554</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571555</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565008</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,8 +1103,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>